--- a/MEME manual annotations.xlsx
+++ b/MEME manual annotations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10E3F7AE-E768-5745-9C98-BF08EC0B3BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC81E372-4697-0448-82CF-383D040B701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="800" windowWidth="18660" windowHeight="16940" xr2:uid="{7AA2DFE4-5D5E-2F4D-BE0F-FA5793F0E76F}"/>
+    <workbookView xWindow="15640" yWindow="760" windowWidth="13760" windowHeight="18360" xr2:uid="{7AA2DFE4-5D5E-2F4D-BE0F-FA5793F0E76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="81">
   <si>
     <t>meme folder</t>
   </si>
@@ -50,15 +50,6 @@
     <t>GTCA</t>
   </si>
   <si>
-    <t>g1</t>
-  </si>
-  <si>
-    <t>g2</t>
-  </si>
-  <si>
-    <t>interocular annotation</t>
-  </si>
-  <si>
     <t>GTAAA</t>
   </si>
   <si>
@@ -80,18 +71,12 @@
     <t>Result</t>
   </si>
   <si>
-    <t xml:space="preserve">conflict </t>
-  </si>
-  <si>
     <t>CTCGC</t>
   </si>
   <si>
     <t>GCGAG</t>
   </si>
   <si>
-    <t>algo improved</t>
-  </si>
-  <si>
     <t xml:space="preserve">IR </t>
   </si>
   <si>
@@ -99,19 +84,220 @@
   </si>
   <si>
     <t>short or poly-n's algo</t>
+  </si>
+  <si>
+    <t>TTCA</t>
+  </si>
+  <si>
+    <t>TACC</t>
+  </si>
+  <si>
+    <t>GGTA</t>
+  </si>
+  <si>
+    <t>ATTAC</t>
+  </si>
+  <si>
+    <t>GTAAT</t>
+  </si>
+  <si>
+    <t>TGTAATGTT</t>
+  </si>
+  <si>
+    <t>CATTACAA</t>
+  </si>
+  <si>
+    <t>algo shorter (subjective)</t>
+  </si>
+  <si>
+    <t>Interocular Annotation</t>
+  </si>
+  <si>
+    <t>GGCTCGC</t>
+  </si>
+  <si>
+    <t>GCGAGCC</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>TCTTAA</t>
+  </si>
+  <si>
+    <t>algo found longer</t>
+  </si>
+  <si>
+    <t>possible conflict , algo blind</t>
+  </si>
+  <si>
+    <t>GGTTTA</t>
+  </si>
+  <si>
+    <t>TAAACC</t>
+  </si>
+  <si>
+    <t>IO g1</t>
+  </si>
+  <si>
+    <t>group1</t>
+  </si>
+  <si>
+    <t>group2</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>AGC</t>
+  </si>
+  <si>
+    <t>GCT</t>
+  </si>
+  <si>
+    <t>TTGTAA</t>
+  </si>
+  <si>
+    <t>TTACAA</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>TTT</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>AT</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>TGA</t>
+  </si>
+  <si>
+    <t>TCA</t>
+  </si>
+  <si>
+    <t>TTAAG</t>
+  </si>
+  <si>
+    <t>TTAAC</t>
+  </si>
+  <si>
+    <t>ACC</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>GT</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>TGTA</t>
+  </si>
+  <si>
+    <t>TACA</t>
+  </si>
+  <si>
+    <t>TGCAC</t>
+  </si>
+  <si>
+    <t>GTGCA</t>
+  </si>
+  <si>
+    <t>TTCC</t>
+  </si>
+  <si>
+    <t>GGAA</t>
+  </si>
+  <si>
+    <t>TAGA</t>
+  </si>
+  <si>
+    <t>TCTA</t>
+  </si>
+  <si>
+    <t>TAT</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>AAAA</t>
+  </si>
+  <si>
+    <t>TTTT</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>GTCAA</t>
+  </si>
+  <si>
+    <t>TTGAC</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Analyzed Direction</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Reverse</t>
+  </si>
+  <si>
+    <t>borderline sig at 0.05</t>
+  </si>
+  <si>
+    <t>TGCACCA</t>
+  </si>
+  <si>
+    <t>TGGTGCA</t>
+  </si>
+  <si>
+    <t>mismatched Algorithm Direct Repeat shows TTAAG….TTAAC … because G/C roughly equally conserved at terminal position -- ambiguous case of both IR and DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mismatched DR from algo - </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -128,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,13 +322,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,10 +682,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B363A8C2-B03D-FD4A-8E52-8E4D9BDA7EAA}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="7" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,19 +696,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -516,8 +736,23 @@
       <c r="E2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>5.0179928028788477E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -528,13 +763,25 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -542,13 +789,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <v>0.23730507796881251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -556,19 +812,31 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -579,16 +847,28 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>0.13614554178328669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -596,19 +876,31 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -616,13 +908,25 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8">
+        <v>0.14594162335065969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -630,13 +934,25 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9">
+        <v>0.2265093962415034</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -644,13 +960,25 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>0.31507397041183532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -658,250 +986,809 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11">
+        <v>0.4832067173130748</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12">
+        <v>0.1883246701319472</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13">
+        <v>5.9976009596161535E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>1.5993602558976409E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
       <c r="B18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18">
+        <v>0.14734106357457019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
         <v>2</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19">
+        <v>3.9984006397441018E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20">
+        <v>0.5549780087964814</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
       <c r="B21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21">
+        <v>0.20311875249900041</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22">
+        <v>0.60815673730507802</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23">
+        <v>3.8584566173530593E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24">
+        <v>0.32207117153138742</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>3</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26">
+        <v>0.1927229108356657</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>3</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27">
+        <v>4.0183926429428231E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>3</v>
       </c>
       <c r="B28">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28">
+        <v>2.7189124350259899E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>3</v>
       </c>
       <c r="B29">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29">
+        <v>0.1597361055577769</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>3</v>
       </c>
       <c r="B30">
         <v>9</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>0.42982806877249102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31">
+        <v>3.7185125949620153E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>4</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32">
+        <v>7.1971211515393846E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J33">
+        <v>0.3744502199120352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34">
+        <v>9.9960015993602559E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35">
+        <v>3.5385845661735298E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s">
+        <v>67</v>
+      </c>
+      <c r="I36" t="s">
+        <v>68</v>
+      </c>
+      <c r="J36">
+        <v>1.9992003198720509E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" t="s">
+        <v>57</v>
+      </c>
+      <c r="J37">
+        <v>3.9984006397441018E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>4</v>
       </c>
       <c r="B38">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s">
+        <v>69</v>
+      </c>
+      <c r="I38" t="s">
+        <v>70</v>
+      </c>
+      <c r="J38">
+        <v>4.3982407037185117E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39">
+        <v>0.59496201519392244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>4</v>
       </c>
       <c r="B40">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>74</v>
+      </c>
+      <c r="H40" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40">
+        <v>0.50819672131147542</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>4</v>
       </c>
       <c r="B41">
         <v>10</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s">
+        <v>72</v>
+      </c>
+      <c r="I41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41">
+        <v>7.2171131547381043E-2</v>
       </c>
     </row>
   </sheetData>

--- a/MEME manual annotations.xlsx
+++ b/MEME manual annotations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC81E372-4697-0448-82CF-383D040B701F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37520687-95FE-4F48-8E2A-841F655509B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15640" yWindow="760" windowWidth="13760" windowHeight="18360" xr2:uid="{7AA2DFE4-5D5E-2F4D-BE0F-FA5793F0E76F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{7AA2DFE4-5D5E-2F4D-BE0F-FA5793F0E76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,8 +299,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,6 +317,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,10 +357,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,6 +698,7 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
     <col min="6" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
@@ -695,7 +709,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D1" t="s">
@@ -707,16 +721,16 @@
       <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1202,22 +1216,21 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+      <c r="A19">
         <v>2</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>8</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="2"/>
       <c r="G19" t="s">
         <v>75</v>
       </c>
@@ -1238,7 +1251,7 @@
       <c r="B20">
         <v>9</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>5</v>
       </c>
       <c r="G20" t="s">
@@ -1261,7 +1274,7 @@
       <c r="B21">
         <v>10</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="G21" t="s">
@@ -1284,7 +1297,7 @@
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
@@ -1307,7 +1320,7 @@
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
@@ -1333,7 +1346,7 @@
       <c r="B24">
         <v>3</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>5</v>
       </c>
       <c r="G24" t="s">
@@ -1356,7 +1369,7 @@
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>6</v>
       </c>
       <c r="D25" t="s">
@@ -1388,7 +1401,7 @@
       <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
@@ -1411,7 +1424,7 @@
       <c r="B27">
         <v>6</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>6</v>
       </c>
       <c r="D27" t="s">
@@ -1443,7 +1456,7 @@
       <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>6</v>
       </c>
       <c r="D28" t="s">
@@ -1472,7 +1485,7 @@
       <c r="B29">
         <v>8</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="G29" t="s">
@@ -1495,7 +1508,7 @@
       <c r="B30">
         <v>9</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>5</v>
       </c>
       <c r="G30" t="s">
@@ -1518,7 +1531,7 @@
       <c r="B31">
         <v>10</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>5</v>
       </c>
       <c r="F31" t="s">
@@ -1544,7 +1557,7 @@
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>5</v>
       </c>
       <c r="F32" t="s">
@@ -1570,7 +1583,7 @@
       <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>5</v>
       </c>
       <c r="G33" t="s">
@@ -1593,7 +1606,7 @@
       <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>5</v>
       </c>
       <c r="G34" t="s">
@@ -1616,7 +1629,7 @@
       <c r="B35">
         <v>4</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>5</v>
       </c>
       <c r="F35" t="s">
@@ -1642,7 +1655,7 @@
       <c r="B36">
         <v>5</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>6</v>
       </c>
       <c r="D36" t="s">
@@ -1671,7 +1684,7 @@
       <c r="B37">
         <v>6</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>6</v>
       </c>
       <c r="D37" t="s">
@@ -1703,7 +1716,7 @@
       <c r="B38">
         <v>7</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>5</v>
       </c>
       <c r="F38" t="s">
@@ -1729,7 +1742,7 @@
       <c r="B39">
         <v>8</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>5</v>
       </c>
       <c r="G39" t="s">
@@ -1752,7 +1765,7 @@
       <c r="B40">
         <v>9</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>5</v>
       </c>
       <c r="G40" t="s">
@@ -1775,7 +1788,7 @@
       <c r="B41">
         <v>10</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>5</v>
       </c>
       <c r="G41" t="s">

--- a/MEME manual annotations.xlsx
+++ b/MEME manual annotations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37520687-95FE-4F48-8E2A-841F655509B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56D4B67-AFBC-CE46-9C61-4351C1ED9F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{7AA2DFE4-5D5E-2F4D-BE0F-FA5793F0E76F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="80">
   <si>
     <t>meme folder</t>
   </si>
@@ -110,18 +110,12 @@
     <t>algo shorter (subjective)</t>
   </si>
   <si>
-    <t>Interocular Annotation</t>
-  </si>
-  <si>
     <t>GGCTCGC</t>
   </si>
   <si>
     <t>GCGAGCC</t>
   </si>
   <si>
-    <t>Both</t>
-  </si>
-  <si>
     <t>TCTTAA</t>
   </si>
   <si>
@@ -279,6 +273,9 @@
   </si>
   <si>
     <t xml:space="preserve">mismatched DR from algo - </t>
+  </si>
+  <si>
+    <t>ManualAnnotation</t>
   </si>
 </sst>
 </file>
@@ -710,28 +707,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -751,10 +748,10 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
         <v>3</v>
@@ -783,7 +780,7 @@
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
         <v>4</v>
@@ -806,13 +803,13 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>0.23730507796881251</v>
@@ -835,16 +832,16 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>1.9992003198720509E-4</v>
@@ -867,16 +864,16 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J6">
         <v>0.13614554178328669</v>
@@ -899,16 +896,16 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
         <v>25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
       </c>
       <c r="J7">
         <v>1.9992003198720509E-4</v>
@@ -928,13 +925,13 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J8">
         <v>0.14594162335065969</v>
@@ -954,13 +951,13 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9">
         <v>0.2265093962415034</v>
@@ -980,13 +977,13 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10">
         <v>0.31507397041183532</v>
@@ -1006,13 +1003,13 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J11">
         <v>0.4832067173130748</v>
@@ -1029,13 +1026,13 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J12">
         <v>0.1883246701319472</v>
@@ -1058,7 +1055,7 @@
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1087,7 +1084,7 @@
         <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1119,7 +1116,7 @@
         <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -1142,19 +1139,19 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
         <v>25</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
       </c>
       <c r="J16">
         <v>1.9992003198720509E-4</v>
@@ -1168,25 +1165,25 @@
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J17">
         <v>1.9992003198720509E-4</v>
@@ -1203,13 +1200,13 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J18">
         <v>0.14734106357457019</v>
@@ -1226,19 +1223,19 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J19">
         <v>3.9984006397441018E-4</v>
@@ -1255,13 +1252,13 @@
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J20">
         <v>0.5549780087964814</v>
@@ -1278,13 +1275,13 @@
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J21">
         <v>0.20311875249900041</v>
@@ -1301,13 +1298,13 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J22">
         <v>0.60815673730507802</v>
@@ -1324,16 +1321,16 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J23">
         <v>3.8584566173530593E-2</v>
@@ -1350,13 +1347,13 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J24">
         <v>0.32207117153138742</v>
@@ -1373,22 +1370,22 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s">
         <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J25">
         <v>1.9992003198720509E-4</v>
@@ -1405,13 +1402,13 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J26">
         <v>0.1927229108356657</v>
@@ -1428,22 +1425,22 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J27">
         <v>4.0183926429428231E-2</v>
@@ -1460,19 +1457,19 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J28">
         <v>2.7189124350259899E-2</v>
@@ -1489,13 +1486,13 @@
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J29">
         <v>0.1597361055577769</v>
@@ -1512,13 +1509,13 @@
         <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J30">
         <v>0.42982806877249102</v>
@@ -1538,13 +1535,13 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J31">
         <v>3.7185125949620153E-2</v>
@@ -1561,16 +1558,16 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J32">
         <v>7.1971211515393846E-2</v>
@@ -1587,13 +1584,13 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J33">
         <v>0.3744502199120352</v>
@@ -1610,13 +1607,13 @@
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J34">
         <v>9.9960015993602559E-4</v>
@@ -1633,16 +1630,16 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J35">
         <v>3.5385845661735298E-2</v>
@@ -1659,19 +1656,19 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J36">
         <v>1.9992003198720509E-4</v>
@@ -1688,22 +1685,22 @@
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J37">
         <v>3.9984006397441018E-4</v>
@@ -1720,16 +1717,16 @@
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J38">
         <v>4.3982407037185117E-2</v>
@@ -1746,13 +1743,13 @@
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J39">
         <v>0.59496201519392244</v>
@@ -1769,13 +1766,13 @@
         <v>5</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J40">
         <v>0.50819672131147542</v>
@@ -1792,13 +1789,13 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I41" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J41">
         <v>7.2171131547381043E-2</v>
